--- a/PTBR/Lang/PTBR/Data/god_talk.xlsx
+++ b/PTBR/Lang/PTBR/Data/god_talk.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -28,16 +28,19 @@
     <font>
       <name val="Arial"/>
       <charset val="128"/>
+      <family val="0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="128"/>
+      <family val="0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="128"/>
+      <family val="0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -80,64 +83,107 @@
     </border>
   </borders>
   <cellStyleXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="20"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment wrapText="1"/>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="20"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -146,7 +192,7 @@
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Excel Built-in Normal" xfId="6" builtinId="0"/>
+    <cellStyle name="Excel Built-in Normal" xfId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -327,12 +373,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="12.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.14" customWidth="1" style="15" min="1" max="1"/>
     <col width="44.42" customWidth="1" style="15" min="2" max="2"/>
@@ -483,15 +529,19 @@
           <t>Bem-vindo... Eu tenho... Expectativas sobre você...</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L3" s="18" t="inlineStr">
@@ -504,12 +554,11 @@
           <t>Oh, quem temos aqui? Sirva-me bem, e eu cuidarei de você.</t>
         </is>
       </c>
-      <c r="N3" s="21" t="inlineStr">
+      <c r="N3" s="22" t="inlineStr">
         <is>
           <t>Um novo seguidor, hein? Escolha interessante.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="57.45" customFormat="1" customHeight="1" s="15">
       <c r="A4" s="17" t="inlineStr">
@@ -541,7 +590,7 @@
 Você é um paradigma entre os fiéis.</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Miau miau miau miaau!
 Mewewewewewew!
@@ -573,15 +622,19 @@
 Que bom...</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L4" s="19" t="inlineStr">
@@ -600,14 +653,13 @@
 Obrigado, meu adorável mortal.</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="N4" s="22" t="inlineStr">
         <is>
           <t>Ah, belo presente. Muito apreciado.
 Não me importo com o presente, mas certifique-se de gastar também com equipamentos, tudo bem?
 Interessante. Agradeço.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A5" s="17" t="inlineStr">
@@ -650,15 +702,19 @@
           <t>Aqui... Tnho algo para... Você...</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
@@ -671,12 +727,11 @@
           <t>Que isso te sirva como você me serviu, meu querido mortal.</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="N5" s="22" t="inlineStr">
         <is>
           <t>Seus esforços não passaram despercebidos. Aqui está algo para reconhecer isso.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A6" s="17" t="inlineStr">
@@ -719,15 +774,19 @@
           <t>Um traidor... Eu não posso tolerar...</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L6" s="18" t="inlineStr">
@@ -740,12 +799,11 @@
           <t>Fico triste em ver você partir...</t>
         </is>
       </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>Sabe, eu estava começando a gostar de você. Mas, bem, chegou a hora de mostrar minha ira divina.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A7" s="17" t="inlineStr">
@@ -788,15 +846,19 @@
           <t>Bom trabalho... De verdade...</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L7" s="18" t="inlineStr">
@@ -809,12 +871,11 @@
           <t>Você fez tão bem, meu adorável mortal. Vou te afagar a cabeça como recompensa.</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>Mhm, bom trabalho.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A8" s="17" t="inlineStr">
@@ -857,15 +918,19 @@
           <t>Eu... Não terei misericórdia com meus inimigos.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L8" s="18" t="inlineStr">
@@ -878,12 +943,11 @@
           <t>Que fofo. Achou que seria tão fácil?</t>
         </is>
       </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="N8" s="22" t="inlineStr">
         <is>
           <t>Ah, uma tentativa medíocre.</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A9" s="17" t="inlineStr">
@@ -926,15 +990,19 @@
           <t>Você é... Meu precioso mortal...</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L9" s="19" t="inlineStr">
@@ -947,12 +1015,11 @@
           <t>Você deseja tocar minha cauda? … Sim, pode.</t>
         </is>
       </c>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="N9" s="22" t="inlineStr">
         <is>
           <t>Assistir você faz o tempo passar rápido.</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A10" s="17" t="inlineStr">
@@ -995,15 +1062,19 @@
           <t>Eu não deixarei você ir... Até que você morra...</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L10" s="18" t="inlineStr">
@@ -1016,12 +1087,11 @@
           <t>Venha aqui, meu servo mais querido. Vou te envolver com minha cauda.</t>
         </is>
       </c>
-      <c r="N10" s="21" t="inlineStr">
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>Normalmente não tenho favoritos, mas você é especial.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A11" s="17" t="inlineStr">
@@ -1064,15 +1134,19 @@
           <t>Bem-vindo de volta... Eu estava esperando por você.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L11" s="18" t="inlineStr">
@@ -1085,12 +1159,11 @@
           <t>Ah, você voltou. Meu abraço está sempre aberto para você.</t>
         </is>
       </c>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="N11" s="22" t="inlineStr">
         <is>
           <t>Bem na hora. Eu já estava ficando entediado.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A12" s="17" t="inlineStr">
@@ -1133,15 +1206,19 @@
           <t>Boa noite... Que um broto brilhante nasça amanhã...</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L12" s="18" t="inlineStr">
@@ -1154,12 +1231,11 @@
           <t>Que a sombra da lua te traga descanso, envolto em meu carinho.</t>
         </is>
       </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="N12" s="22" t="inlineStr">
         <is>
           <t>Coma bem e durma bem. Simples, mas crucial para superar desafios.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="57.45" customFormat="1" customHeight="1" s="15">
       <c r="A13" s="17" t="inlineStr">
@@ -1216,15 +1292,19 @@
 … Está satisfeito agora?</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L13" s="19" t="inlineStr">
@@ -1245,7 +1325,7 @@
 Que pena, nunca deveriam ter tocado no meu/minha filho(a).</t>
         </is>
       </c>
-      <c r="N13" s="21" t="inlineStr">
+      <c r="N13" s="22" t="inlineStr">
         <is>
           <t>Que divertido! Exatamente como um combate deveria ser.
 Boas habilidades. Você realmente é intrigante.
@@ -1254,7 +1334,6 @@
 Parece que está ganhando uma experiência valiosa. Como deveria!</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14" ht="102.2" customFormat="1" customHeight="1" s="15">
       <c r="A14" s="17" t="inlineStr">
@@ -1310,15 +1389,19 @@
 Eu darei... Mais do que você precisa.</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L14" s="19" t="inlineStr">
@@ -1338,7 +1421,7 @@
 Kizuami é um irmão mais velho tão confiável, embora ele seja um pouco malvado às vezes.</t>
         </is>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="22" t="inlineStr">
         <is>
           <t>Mhm, à fé pode ser decisiva em algumas batalhas. Eu vou lhe dar uma mão quando você precisar.
 Precisa de ajuda? Pode contar comigo.
@@ -1348,10 +1431,9 @@
 Você faz questão de seguir seu próprio caminho. Nada mais divertido para mim do que isso.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15" ht="91" customHeight="1" s="16">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>chat</t>
         </is>
@@ -1421,15 +1503,19 @@
 Flores... E você… Eventualmente ficarão ficar juntos...</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L15" s="19" t="inlineStr">
@@ -1449,17 +1535,16 @@
 Você não tem nada a temer, meu/minha fiel servo(a). Eu não deixarei ninguém te machucar.</t>
         </is>
       </c>
-      <c r="N15" s="21" t="inlineStr">
+      <c r="N15" s="22" t="inlineStr">
         <is>
           <t>Eu tenho muito respeito por Kumiromi e Jure. Afinal, não se pode aproveitar um combate saudável sem suprimentos e remédios._x000D_
 Essa cicatriz no meu olho? Bem, é como um distintivo de honra._x000D_
 Assistir você me faz querer voltar para o campo de batalha.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16" ht="35.05" customHeight="1" s="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>reward</t>
         </is>
@@ -1507,15 +1592,19 @@
 Isso mesmo…</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L16" s="19" t="inlineStr">
@@ -1530,21 +1619,20 @@
 Aqui, não perca, tudo bem?</t>
         </is>
       </c>
-      <c r="N16" s="21" t="inlineStr">
+      <c r="N16" s="22" t="inlineStr">
         <is>
           <t>Não é que eu queira facilitar as coisas para você, mas você merece._x000D_
 Vai ser divertido ver como você vai utilizar isso.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17" ht="35.05" customHeight="1" s="16">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>ability</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" s="21" t="n"/>
       <c r="C17" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Torne-se o vento!  
@@ -1559,8 +1647,8 @@
 Faça bom uso disso.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
       <c r="G17" s="19" t="inlineStr">
         <is>
           <t>Ilumine essa alma ferida com a luz da cura!
@@ -1568,16 +1656,20 @@
 Sua jornaga não acabará aqui!</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr"/>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K17" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L17" s="19" t="inlineStr">
@@ -1587,12 +1679,11 @@
 Como você desejar.</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="M17" s="21" t="n"/>
+      <c r="N17" s="21" t="n"/>
     </row>
     <row r="18" ht="23.85" customHeight="1" s="16">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>pet</t>
         </is>
@@ -1602,7 +1693,7 @@
           <t>Android, este mortal cuidará da sua manutenção.</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Lá vai você, anjo negro.  </t>
         </is>
@@ -1632,15 +1723,19 @@
           <t>Adeus, querida fada.</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K18" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="L18" s="18" t="inlineStr">
@@ -1653,12 +1748,11 @@
           <t>Minha empregada raposa, gostaria que você cuidasse deste mortal, assim como como você cuidou de mim.</t>
         </is>
       </c>
-      <c r="N18" s="21" t="inlineStr">
+      <c r="N18" s="22" t="inlineStr">
         <is>
           <t>Dê #pc_him sua força. Não se preocupe, você vai ficar bem.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" s="16">
       <c r="A19" s="15" t="inlineStr">
@@ -1666,56 +1760,59 @@
           <t>morning</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Acorde.</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ahaha, você tinha um rosto tão adorável enquanto dormia, mortal.  </t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Acorde. Agora!</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>Umimyaa!</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>Muwahahahahaha!</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>A-a-acorde já!</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>Você dormiu bem?</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="21" t="n"/>
+      <c r="N19" s="21" t="n"/>
     </row>
     <row r="20" ht="12.75" customHeight="1" s="16">
       <c r="A20" s="15" t="inlineStr">
@@ -1723,56 +1820,59 @@
           <t>shrine</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Muito bem, use-o.</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Quer isso? Então, implore por isso."  </t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Eu lhe concederei um vislumbre do meu poder.</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>Mewmyaa! Você me encontrou!</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Muwahahaaha! Use isso!</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="26" t="inlineStr">
         <is>
           <t>H-hã? Você quer...? Aqui, um abração...!</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>Isso é para você…</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>Umimya-!</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="21" t="n"/>
+      <c r="N20" s="21" t="n"/>
     </row>
     <row r="21" ht="32.8" customHeight="1" s="16">
       <c r="A21" s="15" t="inlineStr">
@@ -1780,30 +1880,29 @@
           <t>regards</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>Por favor, seja gentil com minha irmãzinha. Ela realmente faz o melhor que pode.
 Se você for ver a Horome, leve alguns doces, e minhas saudações.</t>
         </is>
       </c>
-      <c r="M21" s="21" t="inlineStr">
+      <c r="M21" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Você vai encontrar o meu irmão? Seja uma boa pessoa, tudo bem?
 Espero que meu irmão goste de você... </t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="N21" s="21" t="n"/>
     </row>
     <row r="22" ht="12.75" customHeight="1" s="16">
       <c r="A22" s="15" t="inlineStr">
@@ -1811,69 +1910,76 @@
           <t>wedding</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Que instituição tola. Muito bem, vou celebrá-la só por hoje.</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>Prender-se assim? Que ridículo, gatinho.</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>Em meu nome, concedo minha bênção a vocês dois.</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Sejam felizes! Felizes!</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>Muahahahahaha!!!</t>
         </is>
       </c>
-      <c r="G22" s="27" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>N-não é que eu esteja com ciúmes nem nada. ...idiota... parabéns…</t>
         </is>
       </c>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>Nunca se soltem... nunca…</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr"/>
-      <c r="J22" s="21" t="inlineStr"/>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="L22" s="27" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="L22" s="28" t="inlineStr">
         <is>
           <t>Vocês têm minha bênção. Vou me abster de travessuras — só por hoje.</t>
         </is>
       </c>
-      <c r="M22" s="27" t="inlineStr">
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>Oh minha nossa, que delícia! Parabéns.</t>
         </is>
       </c>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="N22" s="28" t="inlineStr">
         <is>
           <t>Deixo meus parabéns. Uma conquista admirável para a sua raça.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="1048576" ht="12.8" customHeight="1" s="16"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>